--- a/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
+++ b/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T16:07:27+00:00</t>
+    <t>2026-08-31T20:29:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
+++ b/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:29:59+00:00</t>
+    <t>2026-09-01T08:25:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
+++ b/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:25:15+00:00</t>
+    <t>2026-09-01T09:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
+++ b/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:40:46+00:00</t>
+    <t>2026-09-01T10:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
+++ b/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T10:03:55+00:00</t>
+    <t>2026-09-01T13:17:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
+++ b/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:17:32+00:00</t>
+    <t>2026-09-03T11:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
+++ b/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="521">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:23:31+00:00</t>
+    <t>2026-09-03T16:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -896,6 +896,12 @@
   </si>
   <si>
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
+  &lt;code value="224083004"/&gt;
+&lt;/valueCoding&gt;</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -5438,7 +5444,7 @@
         <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>82</v>
@@ -5477,7 +5483,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5498,10 +5504,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5512,10 +5518,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5541,16 +5547,16 @@
         <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5599,7 +5605,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5620,10 +5626,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5634,10 +5640,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5660,19 +5666,19 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5721,7 +5727,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5736,19 +5742,19 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5756,10 +5762,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5782,16 +5788,16 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5841,7 +5847,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5865,10 +5871,10 @@
         <v>269</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5876,14 +5882,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5902,19 +5908,19 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5963,7 +5969,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5978,19 +5984,19 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -5998,14 +6004,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6024,19 +6030,19 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6085,7 +6091,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6100,19 +6106,19 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6120,10 +6126,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6149,13 +6155,13 @@
         <v>129</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6205,7 +6211,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6226,13 +6232,13 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6240,10 +6246,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6266,17 +6272,17 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6325,7 +6331,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6340,19 +6346,19 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6360,10 +6366,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6389,16 +6395,16 @@
         <v>243</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6435,17 +6441,17 @@
         <v>82</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6454,7 +6460,7 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -6463,30 +6469,30 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>82</v>
@@ -6511,16 +6517,16 @@
         <v>243</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6549,7 +6555,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6567,7 +6573,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6576,7 +6582,7 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>105</v>
@@ -6585,27 +6591,27 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6631,16 +6637,16 @@
         <v>243</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6668,10 +6674,10 @@
         <v>151</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6689,7 +6695,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6698,7 +6704,7 @@
         <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>105</v>
@@ -6713,7 +6719,7 @@
         <v>192</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6724,14 +6730,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6753,16 +6759,16 @@
         <v>243</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6790,10 +6796,10 @@
         <v>151</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6811,7 +6817,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6829,27 +6835,27 @@
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6872,19 +6878,19 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6933,7 +6939,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6954,10 +6960,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6968,10 +6974,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6997,13 +7003,13 @@
         <v>243</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7032,10 +7038,10 @@
         <v>159</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7053,7 +7059,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7071,27 +7077,27 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7117,16 +7123,16 @@
         <v>243</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7154,10 +7160,10 @@
         <v>159</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7175,7 +7181,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7196,10 +7202,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7210,10 +7216,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7236,16 +7242,16 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7295,7 +7301,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7313,27 +7319,27 @@
         <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7356,16 +7362,16 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7415,7 +7421,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7433,27 +7439,27 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7476,19 +7482,19 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7537,7 +7543,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7549,7 +7555,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7558,10 +7564,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7572,10 +7578,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7690,10 +7696,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7810,14 +7816,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7839,10 +7845,10 @@
         <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>117</v>
@@ -7897,7 +7903,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7932,10 +7938,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7958,13 +7964,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8015,7 +8021,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8024,7 +8030,7 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -8036,10 +8042,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8050,10 +8056,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8076,13 +8082,13 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8133,7 +8139,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8142,7 +8148,7 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>105</v>
@@ -8154,10 +8160,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8168,10 +8174,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8197,16 +8203,16 @@
         <v>243</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8234,10 +8240,10 @@
         <v>173</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8255,7 +8261,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8273,13 +8279,13 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8290,10 +8296,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8319,16 +8325,16 @@
         <v>243</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8356,10 +8362,10 @@
         <v>159</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8377,7 +8383,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8395,13 +8401,13 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8412,10 +8418,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8438,17 +8444,17 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8497,7 +8503,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8521,7 +8527,7 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8532,10 +8538,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8561,10 +8567,10 @@
         <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8615,7 +8621,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8636,10 +8642,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8650,10 +8656,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8676,16 +8682,16 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8735,7 +8741,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8756,10 +8762,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8770,10 +8776,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8796,16 +8802,16 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8855,7 +8861,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8876,10 +8882,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8890,10 +8896,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8916,19 +8922,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8977,7 +8983,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8998,10 +9004,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9012,10 +9018,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9130,10 +9136,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9250,14 +9256,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9279,10 +9285,10 @@
         <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>117</v>
@@ -9337,7 +9343,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9372,10 +9378,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9401,13 +9407,13 @@
         <v>243</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>264</v>
@@ -9459,7 +9465,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>93</v>
@@ -9477,7 +9483,7 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>269</v>
@@ -9494,10 +9500,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9520,19 +9526,19 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9581,7 +9587,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9599,27 +9605,27 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9645,16 +9651,16 @@
         <v>243</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9682,10 +9688,10 @@
         <v>151</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9703,7 +9709,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9712,7 +9718,7 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>105</v>
@@ -9727,7 +9733,7 @@
         <v>192</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9738,14 +9744,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9767,16 +9773,16 @@
         <v>243</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9804,10 +9810,10 @@
         <v>151</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -9825,7 +9831,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9843,27 +9849,27 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9889,16 +9895,16 @@
         <v>82</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -9947,7 +9953,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9968,10 +9974,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
+++ b/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T16:19:13+00:00</t>
+    <t>2026-09-08T13:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
+++ b/StructureDefinition-mii-pr-sdd-partnerschaft.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T13:04:20+00:00</t>
+    <t>2026-09-08T13:56:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
